--- a/Config/Config.xlsx
+++ b/Config/Config.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupecgi-my.sharepoint.com/personal/ali_mahjoub_cgi_com/Documents/Documents/UiPath/AI Social Media Manager/Config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{04A6FCC9-2EBC-479D-970D-986588D51F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B629A2F-B48E-48D9-A265-54B66E5280E7}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{04A6FCC9-2EBC-479D-970D-986588D51F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E404BE14-CE9B-49A8-A987-493D9B6AA468}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{054E92E9-8A22-462D-B45F-2085CB9A574B}"/>
+    <workbookView xWindow="4728" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{054E92E9-8A22-462D-B45F-2085CB9A574B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="PostingTimes" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -454,6 +455,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB7BAA03-3F80-48E0-B2DA-F05A6A146C2A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01977AF-9330-4254-BAF1-FDE769D1C557}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -491,7 +501,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
